--- a/data/credit_bond_all_2026-10-13.xlsx
+++ b/data/credit_bond_all_2026-10-13.xlsx
@@ -14048,7 +14048,7 @@
     <row r="60" customHeight="true" ht="18.0">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>26中国银行三农债02</t>
+          <t>26扬州绿产MTN002</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -14058,64 +14058,64 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>2628006.IB</t>
+          <t>102683968.IB</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>20.0</v>
+        <v>3.0</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>100.0</v>
+        <v>3.0</v>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.90</t>
+          <t>1.50 ~ 2.30</t>
         </is>
       </c>
       <c r="H60" s="4" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>29.52</v>
+        <v>45.52</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>25中国银行三农债01</t>
+          <t>25扬州绿产MTN002</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>2.16Y</t>
+          <t>2.10Y+N</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>1.5083</t>
+          <t>1.7272</t>
         </is>
       </c>
       <c r="N60" s="3" t="inlineStr">
         <is>
-          <t>1.5050/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O60" s="3" t="inlineStr">
         <is>
-          <t>中国银行股份有限公司</t>
+          <t>扬州绿色产业投资发展控股(集团)有限责任公司</t>
         </is>
       </c>
       <c r="P60" s="3" t="inlineStr">
         <is>
-          <t>S- 86.68</t>
+          <t>C- 22.72</t>
         </is>
       </c>
       <c r="Q60" s="3" t="inlineStr">
@@ -14125,133 +14125,139 @@
       </c>
       <c r="R60" s="3" t="inlineStr">
         <is>
-          <t>10-13 09:30</t>
+          <t>10-13 09:00</t>
         </is>
       </c>
       <c r="S60" s="3" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="T60" s="3" t="inlineStr">
         <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="U60" s="4" t="n">
+        <v>2.7667</v>
+      </c>
+      <c r="V60" s="4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W60" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X60" s="3" t="inlineStr">
+        <is>
+          <t>1.84%~1.94%</t>
+        </is>
+      </c>
+      <c r="Y60" s="3" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z60" s="3"/>
+      <c r="AA60" s="3" t="inlineStr">
+        <is>
+          <t>江苏省-扬州市</t>
+        </is>
+      </c>
+      <c r="AB60" s="3" t="inlineStr">
+        <is>
+          <t>本期拟发行规模3亿元,拟用于偿还发行人存量债务融资工具本金[23扬州绿产PPN001,23扬州绿产MTN001]</t>
+        </is>
+      </c>
+      <c r="AC60" s="3" t="inlineStr">
+        <is>
+          <t>中信银行股份有限公司,中国邮政储蓄银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD60" s="3" t="inlineStr">
+        <is>
+          <t>扬州经济技术开发区开发(集团)有限公司</t>
+        </is>
+      </c>
+      <c r="AE60" s="3" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="AF60" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AG60" s="3" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="AH60" s="3" t="inlineStr">
+        <is>
+          <t>扬州绿色产业投资发展控股(集团)有限责任公司2026年度第二期中期票据</t>
+        </is>
+      </c>
+      <c r="AI60" s="3" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="AJ60" s="3" t="inlineStr">
+        <is>
+          <t>2029-10-14</t>
+        </is>
+      </c>
+      <c r="AK60" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
+      <c r="AL60" s="3" t="inlineStr">
+        <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="U60" s="4" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="V60" s="3"/>
-      <c r="W60" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X60" s="3" t="inlineStr">
-        <is>
-          <t>1.54%~1.64%</t>
-        </is>
-      </c>
-      <c r="Y60" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z60" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="AA60" s="3" t="inlineStr">
-        <is>
-          <t>北京市</t>
-        </is>
-      </c>
-      <c r="AB60" s="3" t="inlineStr">
-        <is>
-          <t>本期债券募集资金将专项用于发放涉农贷款</t>
-        </is>
-      </c>
-      <c r="AC60" s="3" t="inlineStr">
-        <is>
-          <t>中银国际证券股份有限公司,中国工商银行股份有限公司,中国邮政储蓄银行股份有限公司,兴业银行股份有限公司,招商银行股份有限公司,江苏银行股份有限公司,中信证券股份有限公司,中信建投证券股份有限公司,国泰海通证券股份有限公司,中国国际金融股份有限公司,中国银河证券股份有限公司,申万宏源证券有限公司,东方证券股份有限公司,国开证券股份有限公司,广发证券股份有限公司,国投证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD60" s="3"/>
-      <c r="AE60" s="3" t="inlineStr">
-        <is>
-          <t>商业银行普通债券</t>
-        </is>
-      </c>
-      <c r="AF60" s="3" t="inlineStr">
-        <is>
-          <t>中央国有企业</t>
-        </is>
-      </c>
-      <c r="AG60" s="3" t="inlineStr">
-        <is>
-          <t>银行间</t>
-        </is>
-      </c>
-      <c r="AH60" s="3" t="inlineStr">
-        <is>
-          <t>中国银行股份有限公司2026年"三农"专项金融债券(第一期)(债券通)</t>
-        </is>
-      </c>
-      <c r="AI60" s="3" t="inlineStr">
-        <is>
-          <t>公募</t>
-        </is>
-      </c>
-      <c r="AJ60" s="3" t="inlineStr">
-        <is>
-          <t>2029-10-15</t>
-        </is>
-      </c>
-      <c r="AK60" s="3"/>
-      <c r="AL60" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
       <c r="AM60" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AN60" s="3" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="AO60" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP60" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ60" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR60" s="3" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS60" s="3" t="inlineStr">
         <is>
-          <t>国有银行</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT60" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU60" s="3" t="inlineStr">
@@ -14261,12 +14267,12 @@
       </c>
       <c r="AV60" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW60" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX60" s="3" t="inlineStr">
@@ -14279,12 +14285,14 @@
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="AZ60" s="3"/>
+      <c r="AZ60" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="61" customHeight="true" ht="18.0">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>26扬州绿产MTN002</t>
+          <t>26扬州绿产MTN003</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -14294,7 +14302,7 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>102683968.IB</t>
+          <t>102683973.IB</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
@@ -14303,10 +14311,10 @@
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
@@ -14314,10 +14322,10 @@
         </is>
       </c>
       <c r="H61" s="4" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>45.52</v>
+        <v>46.52</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
@@ -14375,10 +14383,10 @@
         </is>
       </c>
       <c r="U61" s="4" t="n">
-        <v>2.7667</v>
+        <v>2.75</v>
       </c>
       <c r="V61" s="4" t="n">
-        <v>1.25</v>
+        <v>7.0</v>
       </c>
       <c r="W61" s="3" t="inlineStr">
         <is>
@@ -14403,12 +14411,12 @@
       </c>
       <c r="AB61" s="3" t="inlineStr">
         <is>
-          <t>本期拟发行规模3亿元,拟用于偿还发行人存量债务融资工具本金[23扬州绿产PPN001,23扬州绿产MTN001]</t>
+          <t>本期拟发行规模2亿元,拟用于偿还发行人存量债务融资工具[23扬州绿产MTN001]</t>
         </is>
       </c>
       <c r="AC61" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,中国邮政储蓄银行股份有限公司</t>
+          <t>江苏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD61" s="3" t="inlineStr">
@@ -14433,7 +14441,7 @@
       </c>
       <c r="AH61" s="3" t="inlineStr">
         <is>
-          <t>扬州绿色产业投资发展控股(集团)有限责任公司2026年度第二期中期票据</t>
+          <t>扬州绿色产业投资发展控股(集团)有限责任公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI61" s="3" t="inlineStr">
@@ -14528,7 +14536,7 @@
     <row r="62" customHeight="true" ht="18.0">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>26扬州绿产MTN003</t>
+          <t>26中国银行三农债02</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -14538,49 +14546,49 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>102683973.IB</t>
+          <t>2628006.IB</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>2.0</v>
+        <v>20.0</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>2.0</v>
+        <v>100.0</v>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.30</t>
+          <t>1.30 ~ 1.90</t>
         </is>
       </c>
       <c r="H62" s="4" t="n">
-        <v>1.74</v>
+        <v>1.57</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>46.52</v>
+        <v>29.52</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>25扬州绿产MTN002</t>
+          <t>25中国银行三农债01</t>
         </is>
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>2.10Y+N</t>
+          <t>2.16Y</t>
         </is>
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>1.7272</t>
+          <t>1.5083</t>
         </is>
       </c>
       <c r="N62" s="3" t="inlineStr">
@@ -14590,12 +14598,12 @@
       </c>
       <c r="O62" s="3" t="inlineStr">
         <is>
-          <t>扬州绿色产业投资发展控股(集团)有限责任公司</t>
+          <t>中国银行股份有限公司</t>
         </is>
       </c>
       <c r="P62" s="3" t="inlineStr">
         <is>
-          <t>C- 22.72</t>
+          <t>S- 86.68</t>
         </is>
       </c>
       <c r="Q62" s="3" t="inlineStr">
@@ -14605,69 +14613,67 @@
       </c>
       <c r="R62" s="3" t="inlineStr">
         <is>
-          <t>10-13 09:00</t>
+          <t>10-13 09:30</t>
         </is>
       </c>
       <c r="S62" s="3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="T62" s="3" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="U62" s="4" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="V62" s="4" t="n">
-        <v>7.0</v>
-      </c>
+        <v>3.0</v>
+      </c>
+      <c r="V62" s="3"/>
       <c r="W62" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X62" s="3" t="inlineStr">
         <is>
-          <t>1.84%~1.94%</t>
+          <t>1.54%~1.64%</t>
         </is>
       </c>
       <c r="Y62" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="Z62" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z62" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA62" s="3" t="inlineStr">
         <is>
-          <t>江苏省-扬州市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB62" s="3" t="inlineStr">
         <is>
-          <t>本期拟发行规模2亿元,拟用于偿还发行人存量债务融资工具[23扬州绿产MTN001]</t>
+          <t>本期债券募集资金将专项用于发放涉农贷款</t>
         </is>
       </c>
       <c r="AC62" s="3" t="inlineStr">
         <is>
-          <t>江苏银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD62" s="3" t="inlineStr">
-        <is>
-          <t>扬州经济技术开发区开发(集团)有限公司</t>
-        </is>
-      </c>
+          <t>中银国际证券股份有限公司,中国工商银行股份有限公司,中国邮政储蓄银行股份有限公司,兴业银行股份有限公司,招商银行股份有限公司,江苏银行股份有限公司,中信证券股份有限公司,中信建投证券股份有限公司,国泰海通证券股份有限公司,中国国际金融股份有限公司,中国银河证券股份有限公司,申万宏源证券有限公司,东方证券股份有限公司,国开证券股份有限公司,广发证券股份有限公司,国投证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD62" s="3"/>
       <c r="AE62" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF62" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="AG62" s="3" t="inlineStr">
@@ -14677,7 +14683,7 @@
       </c>
       <c r="AH62" s="3" t="inlineStr">
         <is>
-          <t>扬州绿色产业投资发展控股(集团)有限责任公司2026年度第三期中期票据</t>
+          <t>中国银行股份有限公司2026年"三农"专项金融债券(第一期)(债券通)</t>
         </is>
       </c>
       <c r="AI62" s="3" t="inlineStr">
@@ -14687,57 +14693,53 @@
       </c>
       <c r="AJ62" s="3" t="inlineStr">
         <is>
-          <t>2029-10-14</t>
-        </is>
-      </c>
-      <c r="AK62" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-10-15</t>
+        </is>
+      </c>
+      <c r="AK62" s="3"/>
       <c r="AL62" s="3" t="inlineStr">
         <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="AM62" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AN62" s="3" t="inlineStr">
+        <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="AM62" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="AN62" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
       <c r="AO62" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP62" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AQ62" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR62" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS62" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国有银行</t>
         </is>
       </c>
       <c r="AT62" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU62" s="3" t="inlineStr">
@@ -14747,12 +14749,12 @@
       </c>
       <c r="AV62" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW62" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX62" s="3" t="inlineStr">
@@ -14765,9 +14767,7 @@
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="AZ62" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ62" s="3"/>
     </row>
     <row r="63" customHeight="true" ht="18.0">
       <c r="A63" s="3" t="inlineStr">
